--- a/business_forms/038_labor_cost_reconciliation_request_form--business_forms.xlsx
+++ b/business_forms/038_labor_cost_reconciliation_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'project_a',_'value':_1}</t>
+          <t>project_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Project A', 'value': 1}</t>
+          <t>Project A</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'project_b',_'value':_2}</t>
+          <t>project_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Project B', 'value': 2}</t>
+          <t>Project B</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'project_c',_'value':_3}</t>
+          <t>project_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Project C', 'value': 3}</t>
+          <t>Project C</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'january_2019',_'value':_1}</t>
+          <t>january_2019</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'January 2019', 'value': 1}</t>
+          <t>January 2019</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'february_2019',_'value':_2}</t>
+          <t>february_2019</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'February 2019', 'value': 2}</t>
+          <t>February 2019</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'march_2019',_'value':_3}</t>
+          <t>march_2019</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'March 2019', 'value': 3}</t>
+          <t>March 2019</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'john',_'value':_1}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'John', 'value': 1}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'jane',_'value':_2}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Jane', 'value': 2}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'team',_'value':_3}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Team', 'value': 3}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'active',_'value':_1}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Active', 'value': 1}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'inactive',_'value':_2}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive', 'value': 2}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
